--- a/reports/二级子公司D_资产负债表_2025-11.xlsx
+++ b/reports/二级子公司D_资产负债表_2025-11.xlsx
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0</v>
+        <v>2259000</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0</v>
+        <v>2349360</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0</v>
+        <v>2412000</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0</v>
+        <v>2508480</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0</v>
+        <v>2718000</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0</v>
+        <v>2826720</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0</v>
+        <v>3636000</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0</v>
+        <v>3781440</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0</v>
+        <v>3789000</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0</v>
+        <v>3940560</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0</v>
+        <v>3942000</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0</v>
+        <v>4099680</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0</v>
+        <v>4707000</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0</v>
+        <v>4895280</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>168000000</v>
+        <v>191463000</v>
       </c>
       <c r="G29" s="19" t="n"/>
     </row>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0</v>
+        <v>6237000</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0</v>
+        <v>6486480</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="F55" s="19" t="n">
-        <v>1046000000</v>
+        <v>1052237000</v>
       </c>
       <c r="G55" s="19" t="n"/>
     </row>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="F56" s="19" t="n">
-        <v>1214000000</v>
+        <v>1243700000</v>
       </c>
       <c r="G56" s="19" t="n"/>
     </row>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="F60" s="16" t="n">
-        <v>0</v>
+        <v>10674000</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>0</v>
+        <v>11100960</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1">
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="F62" s="16" t="n">
-        <v>0</v>
+        <v>10980000</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>0</v>
+        <v>11419200</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0</v>
+        <v>11898000</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0</v>
+        <v>12373920</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0</v>
+        <v>12051000</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0</v>
+        <v>12533040</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="F70" s="16" t="n">
-        <v>0</v>
+        <v>12204000</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0</v>
+        <v>12692160</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="F78" s="16" t="n">
-        <v>0</v>
+        <v>13428000</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>0</v>
+        <v>13965120</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0</v>
+        <v>13581000</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0</v>
+        <v>14124240</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="F84" s="19" t="n">
-        <v>125000000</v>
+        <v>209816000</v>
       </c>
       <c r="G84" s="19" t="n"/>
     </row>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="F86" s="16" t="n">
-        <v>0</v>
+        <v>14652000</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>0</v>
+        <v>15238080</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="F98" s="19" t="n">
-        <v>223000000</v>
+        <v>237652000</v>
       </c>
       <c r="G98" s="19" t="n"/>
     </row>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="F99" s="19" t="n">
-        <v>348000000</v>
+        <v>447468000</v>
       </c>
       <c r="G99" s="19" t="n"/>
     </row>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="F121" s="16" t="n">
-        <v>216000000</v>
+        <v>146232000</v>
       </c>
       <c r="G121" s="16" t="n">
         <v>495822320</v>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="F122" s="19" t="n">
-        <v>866000000</v>
+        <v>796232000</v>
       </c>
       <c r="G122" s="19" t="n"/>
     </row>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="F124" s="19" t="n">
-        <v>866000000</v>
+        <v>796232000</v>
       </c>
       <c r="G124" s="19" t="n"/>
     </row>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F125" s="25" t="n">
-        <v>1214000000</v>
+        <v>1243700000</v>
       </c>
       <c r="G125" s="25" t="n"/>
     </row>
